--- a/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -489,12 +477,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -535,12 +517,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -555,14 +531,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>9.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -581,12 +551,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -647,37 +611,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>8.800000000000001</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>3.5</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -693,14 +651,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>17.6</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +674,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>11</v>
-      </c>
-      <c r="E16">
-        <v>64.7</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -734,19 +686,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>17.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -762,14 +708,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>4.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +731,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>48.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="20">
@@ -808,60 +754,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>24.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>19.5</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>2.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +817,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>21.4</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -900,14 +834,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>7</v>
-      </c>
-      <c r="E24">
-        <v>50</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -918,19 +846,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>14.3</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -941,19 +863,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E26">
-        <v>14.3</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="27">
@@ -969,14 +891,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>10.5</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="28">
@@ -992,60 +914,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>22</v>
-      </c>
-      <c r="E28">
-        <v>57.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
-      <c r="E29">
-        <v>23.7</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>7.9</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1061,14 +965,8 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>20</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1084,14 +982,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <v>40</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1102,19 +994,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33">
-        <v>30</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1125,19 +1011,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="35">
@@ -1153,14 +1039,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>2.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1176,83 +1062,71 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>24</v>
-      </c>
-      <c r="E36">
-        <v>66.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E38">
-        <v>2.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>2.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1263,19 +1137,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D40">
-        <v>5</v>
-      </c>
-      <c r="E40">
-        <v>22.7</v>
       </c>
     </row>
     <row r="41">
@@ -1286,7 +1154,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1295,10 +1163,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E41">
-        <v>68.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="42">
@@ -1309,7 +1177,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1318,10 +1186,10 @@
         </is>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E42">
-        <v>9.1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="43">
@@ -1337,83 +1205,71 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>40</v>
-      </c>
-      <c r="E44">
-        <v>58.8</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D45">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>26.5</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>6</v>
-      </c>
-      <c r="E46">
-        <v>8.800000000000001</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1424,7 +1280,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1433,10 +1289,10 @@
         </is>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>6.7</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="48">
@@ -1447,7 +1303,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1456,10 +1312,10 @@
         </is>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E48">
-        <v>73.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="49">
@@ -1470,7 +1326,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1479,10 +1335,10 @@
         </is>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="50">
@@ -1498,106 +1354,88 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>20.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>43</v>
-      </c>
-      <c r="E51">
-        <v>58.1</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E52">
-        <v>13.5</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>5</v>
-      </c>
-      <c r="E53">
-        <v>6.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>1.4</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1608,19 +1446,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55">
-        <v>15.8</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1463,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1640,10 +1472,10 @@
         </is>
       </c>
       <c r="D56">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E56">
-        <v>63.2</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="57">
@@ -1654,7 +1486,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1663,10 +1495,10 @@
         </is>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E57">
-        <v>15.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="58">
@@ -1677,30 +1509,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
-        <v>5.3</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1709,21 +1535,21 @@
         </is>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E59">
-        <v>3.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1732,21 +1558,21 @@
         </is>
       </c>
       <c r="D60">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="E60">
-        <v>72.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,33 +1581,33 @@
         </is>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E61">
-        <v>20.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E62">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="63">
@@ -1792,7 +1618,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1801,10 +1627,10 @@
         </is>
       </c>
       <c r="D63">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E63">
-        <v>16.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -1815,7 +1641,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1824,10 +1650,10 @@
         </is>
       </c>
       <c r="D64">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="E64">
-        <v>63.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="65">
@@ -1838,7 +1664,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1847,10 +1673,10 @@
         </is>
       </c>
       <c r="D65">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="E65">
-        <v>15.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="66">
@@ -1861,157 +1687,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E66">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>33</v>
-      </c>
-      <c r="E68">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>237</v>
-      </c>
-      <c r="E69">
-        <v>59.7</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>92</v>
-      </c>
-      <c r="E70">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>30</v>
-      </c>
-      <c r="E71">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>5</v>
-      </c>
-      <c r="E72">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -411,7 +411,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -565,14 +565,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>56.1</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -588,14 +582,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>24.6</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="13">
@@ -611,31 +605,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>12.3</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>12.3</v>
       </c>
     </row>
     <row r="15">
@@ -651,14 +651,8 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>11</v>
-      </c>
-      <c r="E15">
-        <v>64.7</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -674,7 +668,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -686,13 +680,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>11</v>
+      </c>
+      <c r="E17">
+        <v>64.7</v>
       </c>
     </row>
     <row r="18">
@@ -703,19 +703,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>20</v>
-      </c>
-      <c r="E18">
-        <v>48.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -731,14 +725,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
-      <c r="E19">
-        <v>24.4</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -754,54 +742,60 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>22</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>24.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -817,7 +811,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -834,8 +828,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -846,12 +846,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>22</v>
-      </c>
-      <c r="E26">
-        <v>57.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -891,14 +885,8 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27">
-        <v>23.7</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -914,41 +902,53 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>57.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>23.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
     </row>
@@ -1011,19 +1011,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>24</v>
-      </c>
-      <c r="E34">
-        <v>66.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1039,14 +1033,8 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>9</v>
-      </c>
-      <c r="E35">
-        <v>25</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1062,54 +1050,54 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>66.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E37">
-        <v>22.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>15</v>
-      </c>
-      <c r="E38">
-        <v>68.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1125,7 +1113,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1125,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1142,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1163,10 +1151,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E41">
-        <v>58.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="42">
@@ -1177,19 +1165,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D42">
-        <v>18</v>
-      </c>
-      <c r="E42">
-        <v>26.5</v>
       </c>
     </row>
     <row r="43">
@@ -1205,71 +1187,77 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43">
-        <v>8.800000000000001</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>40</v>
+      </c>
+      <c r="E44">
+        <v>58.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E45">
-        <v>73.3</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1280,19 +1268,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>15</v>
-      </c>
-      <c r="E47">
-        <v>20.3</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1303,7 +1285,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1312,10 +1294,10 @@
         </is>
       </c>
       <c r="D48">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>58.1</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="49">
@@ -1326,19 +1308,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D49">
-        <v>10</v>
-      </c>
-      <c r="E49">
-        <v>13.5</v>
       </c>
     </row>
     <row r="50">
@@ -1354,42 +1330,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>10.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1398,44 +1380,56 @@
         </is>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E52">
-        <v>63.2</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>13.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+      <c r="E54">
+        <v>8.1</v>
       </c>
     </row>
     <row r="55">
@@ -1446,12 +1440,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1457,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1472,10 +1466,10 @@
         </is>
       </c>
       <c r="D56">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E56">
-        <v>72.2</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="57">
@@ -1486,19 +1480,13 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D57">
-        <v>11</v>
-      </c>
-      <c r="E57">
-        <v>20.4</v>
       </c>
     </row>
     <row r="58">
@@ -1509,7 +1497,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1521,99 +1509,87 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D59">
-        <v>18</v>
-      </c>
-      <c r="E59">
-        <v>16.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>70</v>
-      </c>
-      <c r="E60">
-        <v>63.6</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D61">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E61">
-        <v>15.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E62">
-        <v>4.5</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1623,14 +1599,8 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>33</v>
-      </c>
-      <c r="E63">
-        <v>8.300000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1641,19 +1611,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>237</v>
-      </c>
-      <c r="E64">
-        <v>59.7</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1664,19 +1628,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D65">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E65">
-        <v>23.2</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="66">
@@ -1687,18 +1651,179 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>70</v>
+      </c>
+      <c r="E66">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>17</v>
+      </c>
+      <c r="E67">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="D66">
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>9</v>
+      </c>
+      <c r="E69">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>237</v>
+      </c>
+      <c r="E71">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>92</v>
+      </c>
+      <c r="E72">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D73">
         <v>35</v>
       </c>
-      <c r="E66">
+      <c r="E73">
         <v>8.800000000000001</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1646,7 +1646,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1692,7 +1692,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
